--- a/public/Excel_Practice_Combined_Starter.xlsx
+++ b/public/Excel_Practice_Combined_Starter.xlsx
@@ -59,7 +59,7 @@
       <color rgb="00856404"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002B579A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -98,6 +103,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -831,6 +837,50 @@
           <t>Right-click cell B2 and add a comment: "Verify January revenue with finance."</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>IMPORT TASK:</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Download Excel_Practice_Import.csv from the same page you got this file. Then: Data → Get Data → From Text/CSV → select that file → Load. Import it into the empty cells below (rows 23-25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1422,7 +1472,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1962,7 +2011,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -2883,8 +2931,6 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -3348,7 +3394,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -3504,7 +3549,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -3864,7 +3908,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
